--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484297_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484297_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. BENNASSAR ROSSELLÓ</t>
+          <t>P. JOVER SANS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7405</v>
+        <v>3.794</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1981</v>
+        <v>2.8067</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5424</v>
+        <v>0.9873</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6373</v>
+        <v>1.5767</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9225</v>
+        <v>1.6311</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7148</v>
+        <v>-0.0545</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5261</v>
+        <v>2.6801</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2717</v>
+        <v>2.5991</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2544</v>
+        <v>0.0809</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8889</v>
+        <v>-1.1034</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3492</v>
+        <v>-0.968</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5397</v>
+        <v>-0.1354</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7814</v>
+        <v>2.1488</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6344</v>
+        <v>0.3811</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3715</v>
+        <v>0.494</v>
       </c>
       <c r="U2" t="n">
-        <v>0.263</v>
+        <v>-0.1129</v>
       </c>
       <c r="V2" t="n">
         <v>0.6642</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2772</v>
+        <v>0.6093</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3869</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. JOVER SANS</t>
+          <t>A. BENNASSAR ROSSELLÓ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6512</v>
+        <v>3.3283</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8273</v>
+        <v>2.8948</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8239</v>
+        <v>0.4335</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5767</v>
+        <v>2.6373</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6311</v>
+        <v>1.9225</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0545</v>
+        <v>0.7148</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6801</v>
+        <v>3.5261</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5991</v>
+        <v>2.2717</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0809</v>
+        <v>1.2544</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1034</v>
+        <v>-0.8889</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.968</v>
+        <v>-0.3492</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1354</v>
+        <v>-0.5397</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1488</v>
+        <v>0.7814</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2383</v>
+        <v>0.2222</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5147</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2763</v>
+        <v>0.154</v>
       </c>
       <c r="V3" t="n">
         <v>0.6642</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0549</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3499</v>
+        <v>2.014</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5097</v>
+        <v>1.6912</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8403</v>
+        <v>0.3228</v>
       </c>
       <c r="G4" t="n">
         <v>-3.41</v>
@@ -766,13 +766,13 @@
         <v>3.1255</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9673</v>
+        <v>0.6314</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1515</v>
+        <v>0.3331</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8158</v>
+        <v>0.2983</v>
       </c>
       <c r="V4" t="n">
         <v>4.5973</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4082</v>
+        <v>1.636</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4339</v>
+        <v>1.5255</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0257</v>
+        <v>0.1105</v>
       </c>
       <c r="G5" t="n">
         <v>-0.5107</v>
@@ -844,13 +844,13 @@
         <v>1.7581</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8391999999999999</v>
+        <v>0.3886</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.773</v>
+        <v>0.3186</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.06619999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0161</v>
+        <v>0.2826</v>
       </c>
       <c r="E6" t="n">
-        <v>0.047</v>
+        <v>0.6131</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0309</v>
+        <v>-0.3305</v>
       </c>
       <c r="G6" t="n">
         <v>0.7725</v>
@@ -922,13 +922,13 @@
         <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.12</v>
+        <v>0.1465</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.2207</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6667999999999999</v>
+        <v>0.3672</v>
       </c>
       <c r="V6" t="n">
         <v>-0.8317</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3398</v>
+        <v>-0.8808</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4894</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8502999999999999</v>
+        <v>-0.7959000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0106</v>
@@ -1000,13 +1000,13 @@
         <v>2.9301</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6845</v>
+        <v>-0.2256</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5364</v>
+        <v>-0.1319</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1482</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0.3321</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.617</v>
+        <v>-1.4615</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7947</v>
+        <v>-0.6936</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8223</v>
+        <v>-0.7678</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2275</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1123</v>
+        <v>0.0433</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1816</v>
+        <v>-0.0805</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0693</v>
+        <v>0.1238</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2772</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8162</v>
+        <v>-1.7967</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.087</v>
+        <v>-1.2582</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7292</v>
+        <v>-0.5386</v>
       </c>
       <c r="G9" t="n">
         <v>-4.0665</v>
@@ -1156,13 +1156,13 @@
         <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2223</v>
+        <v>0.7972</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4015</v>
+        <v>0.4273</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1793</v>
+        <v>0.3699</v>
       </c>
       <c r="V9" t="n">
         <v>0.8865</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. BAUZA MEDINA</t>
+          <t>B. HIDALGO GARRIGUES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2664</v>
+        <v>-3.7388</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7704</v>
+        <v>-3.098</v>
       </c>
       <c r="F10" t="n">
-        <v>0.504</v>
+        <v>-0.6408</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.8341</v>
+        <v>-1.7402</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.8203</v>
+        <v>-2.5088</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0138</v>
+        <v>0.7687</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.2701</v>
+        <v>-0.7623</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.3915</v>
+        <v>-0.857</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1214</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5639</v>
+        <v>-0.9779</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4287</v>
+        <v>-1.6518</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1352</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5443</v>
+        <v>-0.78</v>
       </c>
       <c r="T10" t="n">
-        <v>3.4531</v>
+        <v>-0.3823</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0912</v>
+        <v>-0.3977</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. HIDALGO GARRIGUES</t>
+          <t>A. BAUZA MEDINA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5034</v>
+        <v>-5.4516</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.563</v>
+        <v>-5.8739</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9404</v>
+        <v>0.4223</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7402</v>
+        <v>-5.8341</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.5088</v>
+        <v>-5.8203</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7687</v>
+        <v>-0.0138</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7623</v>
+        <v>-5.2701</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.857</v>
+        <v>-5.3915</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.1214</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9779</v>
+        <v>-0.5639</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.6518</v>
+        <v>-0.4287</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6739000000000001</v>
+        <v>-0.1352</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5446</v>
+        <v>1.3592</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8473000000000001</v>
+        <v>1.3497</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6973</v>
+        <v>0.0095</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0506</v>
+        <v>-6.245</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.6161</v>
+        <v>-5.9194</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4345</v>
+        <v>-0.3256</v>
       </c>
       <c r="G12" t="n">
         <v>-2.1383</v>
@@ -1390,13 +1390,13 @@
         <v>2.1488</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4633</v>
+        <v>0.2689</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4404</v>
+        <v>0.137</v>
       </c>
       <c r="U12" t="n">
-        <v>0.023</v>
+        <v>0.1319</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6642</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.427500000000002</v>
+        <v>-8.519500000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.304600000000001</v>
+        <v>-7.3968</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1227</v>
+        <v>-1.1228</v>
       </c>
       <c r="G13" t="n">
         <v>-13.9514</v>
@@ -1447,7 +1447,7 @@
         <v>-2.502199999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>4.051500000000001</v>
+        <v>4.0515</v>
       </c>
       <c r="M13" t="n">
         <v>-15.5007</v>
@@ -1468,13 +1468,13 @@
         <v>18.5576</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3247</v>
+        <v>3.2328</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4046</v>
+        <v>2.3124</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9203999999999998</v>
+        <v>0.9203000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>4.152600000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>M. BATALLER LOPEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.7708</v>
+        <v>7.8421</v>
       </c>
       <c r="E14" t="n">
-        <v>5.1957</v>
+        <v>4.9308</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5751</v>
+        <v>2.9113</v>
       </c>
       <c r="G14" t="n">
-        <v>4.5095</v>
+        <v>4.0298</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8895</v>
+        <v>2.0476</v>
       </c>
       <c r="I14" t="n">
-        <v>0.62</v>
+        <v>1.9822</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9899</v>
+        <v>4.1944</v>
       </c>
       <c r="K14" t="n">
-        <v>3.909</v>
+        <v>2.2116</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0809</v>
+        <v>1.9828</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5197000000000001</v>
+        <v>-0.1645</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0194</v>
+        <v>-0.1639</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5391</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7581</v>
+        <v>2.9301</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5385</v>
+        <v>0.121</v>
       </c>
       <c r="T14" t="n">
-        <v>1.296</v>
+        <v>-0.0246</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2425</v>
+        <v>0.1457</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9414</v>
+        <v>2.7145</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8865</v>
+        <v>2.7145</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.5974</v>
+        <v>6.7778</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1219</v>
+        <v>4.2857</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4755</v>
+        <v>2.492</v>
       </c>
       <c r="G15" t="n">
-        <v>4.0298</v>
+        <v>4.5095</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0476</v>
+        <v>3.8895</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9822</v>
+        <v>0.62</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1944</v>
+        <v>3.9899</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2116</v>
+        <v>3.909</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9828</v>
+        <v>0.0809</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1645</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1639</v>
+        <v>-0.0194</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.5391</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9301</v>
+        <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1236</v>
+        <v>0.5454</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8335</v>
+        <v>0.386</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2901</v>
+        <v>0.1594</v>
       </c>
       <c r="V15" t="n">
-        <v>2.7145</v>
+        <v>0.9414</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7145</v>
+        <v>0.8865</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.6742</v>
+        <v>3.4979</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5794</v>
+        <v>1.3771</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0949</v>
+        <v>2.1208</v>
       </c>
       <c r="G16" t="n">
         <v>3.1315</v>
@@ -1702,13 +1702,13 @@
         <v>2.9301</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4721</v>
+        <v>0.2957</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3331</v>
+        <v>0.1309</v>
       </c>
       <c r="U16" t="n">
-        <v>0.139</v>
+        <v>0.1649</v>
       </c>
       <c r="V16" t="n">
         <v>-1.8828</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4237</v>
+        <v>2.9916</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9628</v>
+        <v>1.3673</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4609</v>
+        <v>1.6243</v>
       </c>
       <c r="G17" t="n">
         <v>2.5315</v>
@@ -1780,13 +1780,13 @@
         <v>2.5395</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3933</v>
+        <v>-0.8254</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0289</v>
+        <v>-0.6244</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3644</v>
+        <v>-0.201</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2772</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0306</v>
+        <v>2.5893</v>
       </c>
       <c r="E18" t="n">
-        <v>3.1717</v>
+        <v>3.6773</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1411</v>
+        <v>-1.088</v>
       </c>
       <c r="G18" t="n">
         <v>4.068</v>
@@ -1858,13 +1858,13 @@
         <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5099</v>
+        <v>-0.9513</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.271</v>
+        <v>-0.7654</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.239</v>
+        <v>-0.1858</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3321</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2141</v>
+        <v>0.3373</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1219</v>
+        <v>-0.3241</v>
       </c>
       <c r="F19" t="n">
-        <v>0.336</v>
+        <v>0.6614</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8473000000000001</v>
@@ -1936,13 +1936,13 @@
         <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1079</v>
+        <v>0.2311</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5752</v>
+        <v>0.3729</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4673</v>
+        <v>-0.1418</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6093</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>B. MARTI CAPELLA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.188</v>
+        <v>-0.242</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9404</v>
+        <v>0.1767</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1284</v>
+        <v>-0.4186</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7685</v>
+        <v>-0.5935</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1625</v>
+        <v>-0.5935</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9308999999999999</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5255</v>
+        <v>0.0205</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1625</v>
+        <v>0.0205</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6879</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2939</v>
+        <v>-0.614</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3249</v>
+        <v>-0.614</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.6188</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6038</v>
+        <v>-0.121</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1145</v>
+        <v>-0.121</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5107</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="W20" t="n">
         <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. MARTI CAPELLA</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.242</v>
+        <v>-0.954</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1767</v>
+        <v>-0.0707</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4186</v>
+        <v>-0.8833</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5935</v>
+        <v>-0.7685</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5935</v>
+        <v>0.1625</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0205</v>
+        <v>0.5255</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0205</v>
+        <v>-0.1625</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.6879</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.614</v>
+        <v>-1.2939</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.614</v>
+        <v>0.3249</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-1.6188</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.121</v>
+        <v>-0.1623</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.121</v>
+        <v>0.1033</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>-0.2656</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2772</v>
+        <v>-0.6093</v>
       </c>
       <c r="W21" t="n">
         <v>0.2772</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6016</v>
+        <v>-1.4164</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1663</v>
+        <v>-2.7618</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5646</v>
+        <v>1.3454</v>
       </c>
       <c r="G22" t="n">
         <v>1.5867</v>
@@ -2170,13 +2170,13 @@
         <v>2.7348</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.06279999999999999</v>
+        <v>0.1224</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.341</v>
+        <v>0.0634</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2782</v>
+        <v>0.059</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3012</v>
+        <v>-5.4646</v>
       </c>
       <c r="E23" t="n">
         <v>-6.0362</v>
       </c>
       <c r="F23" t="n">
-        <v>0.735</v>
+        <v>0.5716</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7388</v>
@@ -2248,13 +2248,13 @@
         <v>1.7581</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2108</v>
+        <v>-0.3742</v>
       </c>
       <c r="T23" t="n">
         <v>-0.1594</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0513</v>
+        <v>-0.2148</v>
       </c>
       <c r="V23" t="n">
         <v>-3.1563</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9506</v>
+        <v>-5.8573</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.7014</v>
+        <v>-5.4992</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2492</v>
+        <v>-0.3581</v>
       </c>
       <c r="G24" t="n">
         <v>-1.9575</v>
@@ -2326,13 +2326,13 @@
         <v>0.7814</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6257</v>
+        <v>-0.5324</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4842</v>
+        <v>-0.282</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1415</v>
+        <v>-0.2504</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2186</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>9.427400000000002</v>
+        <v>10.1017</v>
       </c>
       <c r="E25" t="n">
-        <v>1.122799999999999</v>
+        <v>1.122899999999997</v>
       </c>
       <c r="F25" t="n">
-        <v>8.304699999999999</v>
+        <v>8.978799999999998</v>
       </c>
       <c r="G25" t="n">
         <v>13.9514</v>
@@ -2404,13 +2404,13 @@
         <v>20.5109</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.3248</v>
+        <v>-1.651</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9201999999999998</v>
+        <v>-0.9202999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.4046</v>
+        <v>-0.7303999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-4.1525</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484297_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484297_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>0.0549</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484297_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. BENNASSAR ROSSELLÓ</t>
+          <t>A. BENNASSAR ROSSELLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>0.3869</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484297_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.4996</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484297_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484297_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.8317</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484297_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484297_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484297_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484297_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484297_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484297_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484297_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-5.099699999999999</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484297_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.0549</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484297_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,11 +1790,16 @@
       <c r="X16" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484297_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,28 +1811,28 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9916</v>
+        <v>2.6846</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3673</v>
+        <v>1.0603</v>
       </c>
       <c r="F17" t="n">
         <v>1.6243</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5315</v>
+        <v>2.2245</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8708</v>
+        <v>1.5638</v>
       </c>
       <c r="I17" t="n">
         <v>0.6607</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6912</v>
+        <v>2.3842</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0299</v>
+        <v>1.7229</v>
       </c>
       <c r="L17" t="n">
         <v>0.6613</v>
@@ -1796,6 +1872,11 @@
       </c>
       <c r="X17" t="n">
         <v>-0.5545</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484297_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.1052</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484297_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,11 +2039,16 @@
       <c r="X19" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484297_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. MARTI CAPELLA</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.242</v>
+        <v>0.307</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1767</v>
+        <v>0.307</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4186</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5935</v>
+        <v>0.307</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5935</v>
+        <v>0.307</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0205</v>
+        <v>0.307</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0205</v>
+        <v>0.307</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.121</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.121</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484297_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>B. MARTI CAPELLA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.954</v>
+        <v>-0.242</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0707</v>
+        <v>0.1767</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8833</v>
+        <v>-0.4186</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7685</v>
+        <v>-0.5935</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1625</v>
+        <v>-0.5935</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9308999999999999</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5255</v>
+        <v>0.0205</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1625</v>
+        <v>0.0205</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6879</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2939</v>
+        <v>-0.614</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3249</v>
+        <v>-0.614</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.6188</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1623</v>
+        <v>-0.121</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1033</v>
+        <v>-0.121</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2656</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="W21" t="n">
         <v>0.2772</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484297_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4164</v>
+        <v>-0.954</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7618</v>
+        <v>-0.0707</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3454</v>
+        <v>-0.8833</v>
       </c>
       <c r="G22" t="n">
-        <v>1.5867</v>
+        <v>-0.7685</v>
       </c>
       <c r="H22" t="n">
-        <v>3.2454</v>
+        <v>0.1625</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6587</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>1.8164</v>
+        <v>0.5255</v>
       </c>
       <c r="K22" t="n">
-        <v>3.0699</v>
+        <v>-0.1625</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2535</v>
+        <v>0.6879</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2297</v>
+        <v>-1.2939</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1755</v>
+        <v>0.3249</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4052</v>
+        <v>-1.6188</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.1255</v>
+        <v>0.586</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.8603</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7348</v>
+        <v>1.5627</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1224</v>
+        <v>-0.1623</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0634</v>
+        <v>0.1033</v>
       </c>
       <c r="U22" t="n">
-        <v>0.059</v>
+        <v>-0.2656</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484297_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.4646</v>
+        <v>-1.4164</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.0362</v>
+        <v>-2.7618</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5716</v>
+        <v>1.3454</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.7388</v>
+        <v>1.5867</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1855</v>
+        <v>3.2454</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5533</v>
+        <v>-1.6587</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.2629</v>
+        <v>1.8164</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.7102</v>
+        <v>3.0699</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5527</v>
+        <v>-1.2535</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5241</v>
+        <v>-0.2297</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.1755</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.4052</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1953</v>
+        <v>-3.1255</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9534</v>
+        <v>-5.8603</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7581</v>
+        <v>2.7348</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3742</v>
+        <v>0.1224</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1594</v>
+        <v>0.0634</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2148</v>
+        <v>0.059</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.1563</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-1.6604</v>
+        <v>1.2186</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4959</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484297_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>H. LOUASSA</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.8573</v>
+        <v>-5.4646</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.4992</v>
+        <v>-6.0362</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3581</v>
+        <v>0.5716</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.9575</v>
+        <v>-1.7388</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2047</v>
+        <v>-1.1855</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.7529</v>
+        <v>-0.5533</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.2871</v>
+        <v>-2.2629</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.2648</v>
+        <v>-1.7102</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.0223</v>
+        <v>-0.5527</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3296</v>
+        <v>0.5241</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0601</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2694</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5324</v>
+        <v>-0.3742</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.282</v>
+        <v>-0.1594</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2504</v>
+        <v>-0.2148</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2186</v>
+        <v>-3.1563</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-1.6604</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484297_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>H. LOUASSA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,152 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
+        <v>-5.8573</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-5.4992</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.3581</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.9575</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.2047</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-1.7529</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-2.2871</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.2648</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-2.0223</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.0601</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.5324</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.282</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.2504</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484297_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>10.1017</v>
       </c>
-      <c r="E25" t="n">
-        <v>1.122899999999997</v>
-      </c>
-      <c r="F25" t="n">
+      <c r="E26" t="n">
+        <v>1.1229</v>
+      </c>
+      <c r="F26" t="n">
         <v>8.978799999999998</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G26" t="n">
         <v>13.9514</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H26" t="n">
         <v>16.6489</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I26" t="n">
         <v>-2.6974</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J26" t="n">
         <v>15.5009</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K26" t="n">
         <v>14.1469</v>
       </c>
-      <c r="L25" t="n">
-        <v>1.354</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="L26" t="n">
+        <v>1.354000000000001</v>
+      </c>
+      <c r="M26" t="n">
         <v>-1.5492</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N26" t="n">
         <v>2.5021</v>
       </c>
-      <c r="O25" t="n">
-        <v>-4.051500000000001</v>
-      </c>
-      <c r="P25" t="n">
+      <c r="O26" t="n">
+        <v>-4.0515</v>
+      </c>
+      <c r="P26" t="n">
         <v>1.9533</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q26" t="n">
         <v>-18.5574</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R26" t="n">
         <v>20.5109</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S26" t="n">
         <v>-1.651</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>-0.9202999999999999</v>
       </c>
-      <c r="U25" t="n">
-        <v>-0.7303999999999999</v>
-      </c>
-      <c r="V25" t="n">
+      <c r="U26" t="n">
+        <v>-0.7304</v>
+      </c>
+      <c r="V26" t="n">
         <v>-4.1525</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W26" t="n">
         <v>5.099699999999999</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X26" t="n">
         <v>-9.252300000000002</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
